--- a/output/pdf_financials_xlsx/PDO.xlsx
+++ b/output/pdf_financials_xlsx/PDO.xlsx
@@ -1085,16 +1085,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.177925</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.155725</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.649997</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.242575</v>
       </c>
     </row>
     <row r="35">
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.177925</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.155725</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.649997</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.242575</v>
       </c>
     </row>
     <row r="37">
@@ -1351,16 +1351,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.295704</v>
+        <v>0.117779</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.278692</v>
+        <v>0.122967</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.770719</v>
+        <v>0.120722</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.384869</v>
+        <v>0.142294</v>
       </c>
     </row>
     <row r="49">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/PDO.xlsx
+++ b/output/pdf_financials_xlsx/PDO.xlsx
@@ -1199,16 +1199,16 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>0.095248</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.131248</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.221715</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.102874</v>
       </c>
     </row>
     <row r="41">
@@ -1218,16 +1218,16 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0.277484</v>
+        <v>0.372732</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.370999</v>
+        <v>0.502247</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.633737</v>
+        <v>0.855452</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.905921</v>
+        <v>1.008795</v>
       </c>
     </row>
     <row r="42">
@@ -1351,16 +1351,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.117779</v>
+        <v>0.022531</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.122967</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.120722</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.142294</v>
+        <v>0.03942</v>
       </c>
     </row>
     <row r="49">
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.067299</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.152483</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.052926</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.014871</v>
       </c>
     </row>
     <row r="68">
@@ -1739,16 +1739,16 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0.56913</v>
+        <v>0.636429</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.796271</v>
+        <v>0.948754</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>1.185924</v>
+        <v>1.23885</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.6757919999999999</v>
+        <v>0.690663</v>
       </c>
     </row>
     <row r="69">
@@ -2552,16 +2552,16 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001807</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001819</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.011323</v>
       </c>
     </row>
     <row r="112">
@@ -2650,13 +2650,13 @@
         <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.0374</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.0339</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.023862</v>
       </c>
     </row>
     <row r="117">
@@ -2997,16 +2997,16 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001807</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001819</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.011323</v>
       </c>
     </row>
     <row r="135">
@@ -3016,16 +3016,16 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>0.052363</v>
+        <v>0.050556</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>0.01881</v>
+        <v>0.016991</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>0.25963</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.5049</v>
+        <v>-0.516223</v>
       </c>
     </row>
   </sheetData>
@@ -4450,7 +4450,11 @@
           <t>Purchase of equipment 7</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>-0.001807</v>
       </c>
@@ -4482,7 +4486,11 @@
           <t>Purchase of intangible assets 8</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
